--- a/Customer Churn Analysis.xlsx
+++ b/Customer Churn Analysis.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/184d964e488833dd/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/184d964e488833dd/Documents/Data Analytics/Projects/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB8A8C21-651F-4FFA-8B7C-450DD5FA277F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{BB8A8C21-651F-4FFA-8B7C-450DD5FA277F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED4191CE-4048-4317-9A04-B4B85E02FA0D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6E0AD0F4-69AE-4357-B72A-D1480A6CC8AB}"/>
   </bookViews>
@@ -22,9 +22,8 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
@@ -366,7 +365,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Customer Churn Analysis (prj3).xlsx]Dashboard!PivotTable1</c:name>
+    <c:name>[Customer Churn Analysis.xlsx]Dashboard!PivotTable1</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -772,7 +771,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Customer Churn Analysis (prj3).xlsx]Dashboard!PivotTable3</c:name>
+    <c:name>[Customer Churn Analysis.xlsx]Dashboard!PivotTable3</c:name>
     <c:fmtId val="1"/>
   </c:pivotSource>
   <c:chart>
@@ -1246,7 +1245,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Customer Churn Analysis (prj3).xlsx]Dashboard!PivotTable2</c:name>
+    <c:name>[Customer Churn Analysis.xlsx]Dashboard!PivotTable2</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -3770,15 +3769,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>55417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>568038</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>27710</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3961,16 +3960,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>7620</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>541713</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>146165</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>561802</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>153785</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4154,15 +4153,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>106101</xdr:colOff>
+      <xdr:colOff>729555</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>176513</xdr:rowOff>
+      <xdr:rowOff>162658</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>434050</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>323213</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>170726</xdr:rowOff>
+      <xdr:rowOff>156871</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4185,6 +4184,84 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>13854</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>692727</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>59574</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Rectangle: Rounded Corners 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1BEA460-703C-43E0-83EE-21156A72DB96}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5320145"/>
+          <a:ext cx="3020291" cy="405938"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Monthly Charges vs Churn Analysis </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-IN" sz="1400" b="1">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4497,7 +4574,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C628F154-0C4D-4A50-94A5-3281CE0E0A1F}" name="PivotTable2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Subscription" colHeaderCaption="Churn">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C628F154-0C4D-4A50-94A5-3281CE0E0A1F}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3" rowHeaderCaption="Subscription" colHeaderCaption="Churn">
   <location ref="A33:D38" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -4677,7 +4754,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49A08C3C-09AB-41AB-B2BB-478467EA03EC}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{49A08C3C-09AB-41AB-B2BB-478467EA03EC}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="2">
   <location ref="H10:I15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField dataField="1" showAll="0"/>
@@ -4830,7 +4907,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E515A842-93E8-4287-9619-E9E5112F2627}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E515A842-93E8-4287-9619-E9E5112F2627}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A12:B16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
